--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484230_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484230_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5221</v>
+        <v>5.0277</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8618</v>
+        <v>3.3674</v>
       </c>
       <c r="F2" t="n">
         <v>1.6603</v>
@@ -610,10 +610,10 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3853</v>
+        <v>0.1203</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4842</v>
+        <v>0.0214</v>
       </c>
       <c r="U2" t="n">
         <v>0.0989</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2642</v>
+        <v>3.2496</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2012</v>
+        <v>2.0014</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0629</v>
+        <v>1.2482</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6549</v>
+        <v>2.9208</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0755</v>
+        <v>1.3024</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5794</v>
+        <v>1.6184</v>
       </c>
       <c r="J3" t="n">
-        <v>6.019</v>
+        <v>3.09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9785</v>
+        <v>2.415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>0.6751</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3641</v>
+        <v>-0.1692</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.903</v>
+        <v>-1.1125</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5389</v>
+        <v>0.9433</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.5162</v>
+        <v>0.3907</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7348</v>
+        <v>0.2153</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7886</v>
+        <v>-0.112</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9462</v>
+        <v>0.3272</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.852</v>
+        <v>2.9587</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3859</v>
+        <v>0.4283</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4661</v>
+        <v>2.5305</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9208</v>
+        <v>1.5334</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3024</v>
+        <v>1.9248</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6184</v>
+        <v>-0.3914</v>
       </c>
       <c r="J4" t="n">
-        <v>3.09</v>
+        <v>0.9394</v>
       </c>
       <c r="K4" t="n">
-        <v>2.415</v>
+        <v>1.3303</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6751</v>
+        <v>-0.3908</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1692</v>
+        <v>0.594</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1125</v>
+        <v>0.5946</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9433</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8177</v>
+        <v>0.7146</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2726</v>
+        <v>0.2236</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5451</v>
+        <v>0.491</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>1.8828</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4623</v>
+        <v>2.2633</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4689</v>
+        <v>1.745</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9935</v>
+        <v>0.5182</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5334</v>
+        <v>5.6549</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9248</v>
+        <v>5.0755</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3914</v>
+        <v>0.5794</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9394</v>
+        <v>6.019</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3303</v>
+        <v>5.9785</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3908</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>0.594</v>
+        <v>-0.3641</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5946</v>
+        <v>-0.903</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5389</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1721</v>
+        <v>-3.5162</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2182</v>
+        <v>0.7339</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2642</v>
+        <v>0.3324</v>
       </c>
       <c r="U5" t="n">
-        <v>0.954</v>
+        <v>0.4015</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8828</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7163</v>
+        <v>1.6304</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1288</v>
+        <v>0.3767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8451</v>
+        <v>1.2536</v>
       </c>
       <c r="G6" t="n">
         <v>2.3974</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2904</v>
+        <v>-0.3763</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6052</v>
+        <v>-0.0997</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6852</v>
+        <v>-0.2766</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.677</v>
+        <v>0.7315</v>
       </c>
       <c r="E7" t="n">
         <v>0.0409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6361</v>
+        <v>0.6906</v>
       </c>
       <c r="G7" t="n">
         <v>0.4454</v>
@@ -1000,13 +1000,13 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4612</v>
+        <v>0.53</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0205</v>
+        <v>-1.6814</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4408</v>
+        <v>2.2114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4249</v>
+        <v>1.2619</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2901</v>
+        <v>0.6825</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1348</v>
+        <v>0.5794</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0205</v>
+        <v>0.4728</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>0.4323</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4045</v>
+        <v>0.7891</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2696</v>
+        <v>0.2502</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1348</v>
+        <v>0.5389</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0363</v>
+        <v>0.2448</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2008</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0363</v>
+        <v>0.4456</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. SERRA SÀNCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1195</v>
+        <v>0.5157</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1464</v>
+        <v>0.0205</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2659</v>
+        <v>0.4952</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2619</v>
+        <v>0.4249</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6825</v>
+        <v>0.2901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5794</v>
+        <v>0.1348</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4728</v>
+        <v>0.0205</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4323</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7891</v>
+        <v>0.4045</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2502</v>
+        <v>0.2696</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5389</v>
+        <v>0.1348</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1657</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6657</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5029</v>
+        <v>0.4107</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5563</v>
+        <v>-1.0272</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0592</v>
+        <v>1.438</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5244</v>
+        <v>-0.9649</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.7634</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.458</v>
+        <v>-0.2015</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6792</v>
+        <v>-0.8004</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2714</v>
+        <v>-0.0601</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.7402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1548</v>
+        <v>-0.1645</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2891</v>
+        <v>-0.7032</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1342</v>
+        <v>0.5387</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1876</v>
+        <v>-0.1871</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0221</v>
+        <v>-0.2269</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1655</v>
+        <v>0.0398</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6056</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8345</v>
+        <v>-0.524</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7549</v>
+        <v>0.6169</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9205</v>
+        <v>-1.1409</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9649</v>
+        <v>0.5244</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7634</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2015</v>
+        <v>-0.458</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8004</v>
+        <v>0.6792</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0601</v>
+        <v>1.2714</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7402</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1645</v>
+        <v>-0.1548</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7032</v>
+        <v>-0.2891</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5387</v>
+        <v>0.1342</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4323</v>
+        <v>0.1664</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9546</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4777</v>
+        <v>0.0838</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.6056</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8782</v>
+        <v>-0.8237</v>
       </c>
       <c r="E12" t="n">
         <v>-1.319</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4408</v>
+        <v>0.4952</v>
       </c>
       <c r="G12" t="n">
         <v>1.0389</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.356</v>
+        <v>-3.8615</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5245</v>
+        <v>-4.3023</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1685</v>
+        <v>0.4408</v>
       </c>
       <c r="G13" t="n">
         <v>-2.872</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0467</v>
+        <v>0.4478</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1594</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1127</v>
+        <v>0.385</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8279</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.503</v>
+        <v>12.1084</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.338099999999999</v>
+        <v>0.2672000000000008</v>
       </c>
       <c r="F14" t="n">
-        <v>11.8413</v>
+        <v>11.8411</v>
       </c>
       <c r="G14" t="n">
         <v>14.8818</v>
@@ -1546,13 +1546,13 @@
         <v>11.7205</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7468</v>
+        <v>2.3521</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5216</v>
+        <v>0.08329999999999996</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2684</v>
+        <v>2.2686</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2186</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0197</v>
+        <v>2.1739</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7191</v>
+        <v>0.8202</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3006</v>
+        <v>1.3537</v>
       </c>
       <c r="G15" t="n">
         <v>0.2164</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1271</v>
+        <v>0.2813</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.341</v>
+        <v>-0.2399</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4681</v>
+        <v>0.5212</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9031</v>
+        <v>0.927</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7863</v>
+        <v>0.674</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1169</v>
+        <v>0.253</v>
       </c>
       <c r="G16" t="n">
         <v>2.2236</v>
@@ -1702,13 +1702,13 @@
         <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.82</v>
+        <v>-0.1561</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0072</v>
+        <v>-0.1051</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1872</v>
+        <v>-0.051</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5545</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2812</v>
+        <v>-0.1583</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6697</v>
+        <v>-1.973</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9508</v>
+        <v>1.8147</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8725</v>
@@ -1780,13 +1780,13 @@
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7044</v>
+        <v>0.2648</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3331</v>
+        <v>0.0297</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3713</v>
+        <v>0.2351</v>
       </c>
       <c r="V17" t="n">
         <v>0.2772</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0911</v>
+        <v>-1.1625</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8332</v>
+        <v>-1.6309</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7421</v>
+        <v>0.4684</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5858</v>
@@ -1858,13 +1858,13 @@
         <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.663</v>
+        <v>0.5916</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4015</v>
+        <v>-0.1993</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0646</v>
+        <v>0.7909</v>
       </c>
       <c r="V18" t="n">
         <v>0.2224</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. DÍAZ JIMÉNEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8499</v>
+        <v>-1.7305</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8002</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0498</v>
+        <v>-1.2261</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9953</v>
+        <v>-2.4535</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1471</v>
+        <v>-1.8333</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8482</v>
+        <v>-0.6202</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3065</v>
+        <v>1.0176</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3469</v>
+        <v>-0.1164</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>1.134</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6889</v>
+        <v>-3.471</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1998</v>
+        <v>-1.7168</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8887</v>
+        <v>-1.7542</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>0.618</v>
+        <v>-0.7496</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5063</v>
+        <v>-0.4552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1117</v>
+        <v>-0.2945</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3321</v>
+        <v>0.8865</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>P. DÍAZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7444</v>
+        <v>-1.8901</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1112</v>
+        <v>-1.0024</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6332</v>
+        <v>-0.8877</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4535</v>
+        <v>-2.9953</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8333</v>
+        <v>-1.1471</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6202</v>
+        <v>-1.8482</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0176</v>
+        <v>-1.3065</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1164</v>
+        <v>-1.3469</v>
       </c>
       <c r="L20" t="n">
-        <v>1.134</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.471</v>
+        <v>-1.6889</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7168</v>
+        <v>0.1998</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7542</v>
+        <v>-1.8887</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7635</v>
+        <v>0.5778</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0619</v>
+        <v>0.3041</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7016</v>
+        <v>0.2737</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8865</v>
+        <v>0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0342</v>
+        <v>-2.3003</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1099</v>
+        <v>-2.8156</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0756</v>
+        <v>0.5153</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8682</v>
+        <v>-1.7913</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4508</v>
+        <v>1.3241</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4175</v>
+        <v>-3.1155</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2996</v>
+        <v>-0.4875</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0614</v>
+        <v>2.0875</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.361</v>
+        <v>-2.575</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5686</v>
+        <v>-1.3038</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5121</v>
+        <v>-0.7634</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9435</v>
+        <v>-0.5405</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.166</v>
+        <v>0.1589</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8335</v>
+        <v>-0.3747</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3325</v>
+        <v>0.5336</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1041</v>
+        <v>-2.9137</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3212</v>
+        <v>-2.9077</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2171</v>
+        <v>-0.0061</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7913</v>
+        <v>-1.8682</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3241</v>
+        <v>-1.4508</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1155</v>
+        <v>-0.4175</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4875</v>
+        <v>-1.2996</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0875</v>
+        <v>0.0614</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.575</v>
+        <v>-1.361</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3038</v>
+        <v>-0.5686</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7634</v>
+        <v>-1.5121</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5405</v>
+        <v>0.9435</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6449</v>
+        <v>-1.0455</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8803</v>
+        <v>-0.6313</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2354</v>
+        <v>-0.4142</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8833</v>
+        <v>-3.7743</v>
       </c>
       <c r="E23" t="n">
         <v>-2.5013</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.382</v>
+        <v>-1.273</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7551</v>
@@ -2248,13 +2248,13 @@
         <v>2.3441</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1049</v>
+        <v>-0.9959</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5969</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.508</v>
+        <v>-0.399</v>
       </c>
       <c r="V23" t="n">
         <v>0.6093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.503</v>
+        <v>-10.8288</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.8413</v>
+        <v>-11.8412</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3381000000000005</v>
+        <v>1.0122</v>
       </c>
       <c r="G24" t="n">
         <v>-14.8817</v>
@@ -2326,13 +2326,13 @@
         <v>15.6274</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.746800000000001</v>
+        <v>-1.0727</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2685</v>
+        <v>-2.2686</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5218</v>
+        <v>1.1958</v>
       </c>
       <c r="V24" t="n">
         <v>1.2186</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484230_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484230_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,28 +736,28 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9587</v>
+        <v>2.3447</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4283</v>
+        <v>-0.1857</v>
       </c>
       <c r="F4" t="n">
         <v>2.5305</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5334</v>
+        <v>0.9194</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9248</v>
+        <v>1.3109</v>
       </c>
       <c r="I4" t="n">
         <v>-0.3914</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9394</v>
+        <v>0.3255</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3303</v>
+        <v>0.7163</v>
       </c>
       <c r="L4" t="n">
         <v>-0.3908</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.53</v>
+        <v>0.614</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6814</v>
+        <v>0.614</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2114</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2619</v>
+        <v>0.614</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6825</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5794</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4728</v>
+        <v>0.614</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4323</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7891</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2502</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5389</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2448</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2008</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4456</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5157</v>
+        <v>0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0205</v>
+        <v>-1.6814</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4952</v>
+        <v>2.2114</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4249</v>
+        <v>1.2619</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2901</v>
+        <v>0.6825</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1348</v>
+        <v>0.5794</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0205</v>
+        <v>0.4728</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0205</v>
+        <v>0.4323</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4045</v>
+        <v>0.7891</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2696</v>
+        <v>0.2502</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1348</v>
+        <v>0.5389</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.2448</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.2008</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.4456</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1234,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4107</v>
+        <v>0.5157</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0272</v>
+        <v>0.0205</v>
       </c>
       <c r="F10" t="n">
-        <v>1.438</v>
+        <v>0.4952</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9649</v>
+        <v>0.4249</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7634</v>
+        <v>0.2901</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2015</v>
+        <v>0.1348</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8004</v>
+        <v>0.0205</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0601</v>
+        <v>0.0205</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7402</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1645</v>
+        <v>0.4045</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7032</v>
+        <v>0.2696</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5387</v>
+        <v>0.1348</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1871</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2269</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0398</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.524</v>
+        <v>0.4107</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6169</v>
+        <v>-1.0272</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1409</v>
+        <v>1.438</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5244</v>
+        <v>-0.9649</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.7634</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.458</v>
+        <v>-0.2015</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6792</v>
+        <v>-0.8004</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2714</v>
+        <v>-0.0601</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.7402</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1548</v>
+        <v>-0.1645</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2891</v>
+        <v>-0.7032</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1342</v>
+        <v>0.5387</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1664</v>
+        <v>-0.1871</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.2269</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0838</v>
+        <v>0.0398</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6056</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MONTON MARTÍNEZ</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8237</v>
+        <v>-0.524</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.319</v>
+        <v>0.6169</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4952</v>
+        <v>-1.1409</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0389</v>
+        <v>0.5244</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9041</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1348</v>
+        <v>-0.458</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6344</v>
+        <v>0.6792</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6344</v>
+        <v>1.2714</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4045</v>
+        <v>-0.1548</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2696</v>
+        <v>-0.2891</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1348</v>
+        <v>0.1342</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.1664</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0838</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.6056</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>D. MONTON MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8615</v>
+        <v>-0.8237</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3023</v>
+        <v>-1.319</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4408</v>
+        <v>0.4952</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.872</v>
+        <v>1.0389</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6874</v>
+        <v>0.9041</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.5594</v>
+        <v>0.1348</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.6656</v>
+        <v>0.6344</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2418</v>
+        <v>0.6344</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.4238</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7936</v>
+        <v>0.4045</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9292</v>
+        <v>0.2696</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1356</v>
+        <v>0.1348</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3907</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4478</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.385</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.1084</v>
+        <v>-3.8615</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2672000000000008</v>
+        <v>-4.3023</v>
       </c>
       <c r="F14" t="n">
-        <v>11.8411</v>
+        <v>0.4408</v>
       </c>
       <c r="G14" t="n">
-        <v>14.8818</v>
+        <v>-2.872</v>
       </c>
       <c r="H14" t="n">
-        <v>11.5082</v>
+        <v>0.6874</v>
       </c>
       <c r="I14" t="n">
-        <v>3.373499999999999</v>
+        <v>-3.5594</v>
       </c>
       <c r="J14" t="n">
-        <v>11.7102</v>
+        <v>-3.6656</v>
       </c>
       <c r="K14" t="n">
-        <v>11.7024</v>
+        <v>-0.2418</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008000000000000895</v>
+        <v>-3.4238</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1717</v>
+        <v>0.7936</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1942000000000002</v>
+        <v>0.9292</v>
       </c>
       <c r="O14" t="n">
-        <v>3.365499999999999</v>
+        <v>-0.1356</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.906899999999999</v>
+        <v>0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.6273</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>11.7205</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3521</v>
+        <v>0.4478</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08329999999999996</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2686</v>
+        <v>0.385</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1005</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.3192</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1739</v>
+        <v>12.1084</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8202</v>
+        <v>0.2672000000000017</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3537</v>
+        <v>11.8411</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2164</v>
+        <v>14.8818</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2034</v>
+        <v>11.5083</v>
       </c>
       <c r="I15" t="n">
-        <v>0.013</v>
+        <v>3.3735</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0601</v>
+        <v>11.7103</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7204</v>
+        <v>11.7024</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6603</v>
+        <v>0.008000000000000895</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8437</v>
+        <v>3.1717</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.517</v>
+        <v>-0.1942000000000002</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6733</v>
+        <v>3.365499999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9534</v>
+        <v>-3.906899999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-15.6273</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>11.7205</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2813</v>
+        <v>2.3521</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2399</v>
+        <v>0.08329999999999996</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5212</v>
+        <v>2.2686</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.1005</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-5.3192</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.927</v>
+        <v>2.1739</v>
       </c>
       <c r="E16" t="n">
-        <v>0.674</v>
+        <v>0.8202</v>
       </c>
       <c r="F16" t="n">
-        <v>0.253</v>
+        <v>1.3537</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2236</v>
+        <v>0.2164</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.2034</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3188</v>
+        <v>0.013</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5139</v>
+        <v>1.0601</v>
       </c>
       <c r="K16" t="n">
-        <v>1.352</v>
+        <v>1.7204</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1619</v>
+        <v>-0.6603</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7098</v>
+        <v>-0.8437</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4472</v>
+        <v>-1.517</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1569</v>
+        <v>0.6733</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1561</v>
+        <v>0.2813</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1051</v>
+        <v>-0.2399</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.051</v>
+        <v>0.5212</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7731</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1583</v>
+        <v>0.927</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.973</v>
+        <v>0.674</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8147</v>
+        <v>0.253</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8725</v>
+        <v>2.2236</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.3152</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4428</v>
+        <v>2.3188</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3033</v>
+        <v>1.5139</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9379</v>
+        <v>1.352</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.1619</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5692</v>
+        <v>0.7098</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3773</v>
+        <v>-1.4472</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8081</v>
+        <v>2.1569</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2648</v>
+        <v>-0.1561</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0297</v>
+        <v>-0.1051</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2351</v>
+        <v>-0.051</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>-0.5545</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1625</v>
+        <v>0.921</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6309</v>
+        <v>0.921</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4684</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5858</v>
+        <v>0.921</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5874</v>
+        <v>0.921</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9984</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7201</v>
+        <v>0.921</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2526</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3075</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5916</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1993</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7909</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7305</v>
+        <v>-0.1583</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-1.973</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2261</v>
+        <v>1.8147</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4535</v>
+        <v>-1.8725</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8333</v>
+        <v>-3.3152</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6202</v>
+        <v>1.4428</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0176</v>
+        <v>-1.3033</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1164</v>
+        <v>-1.9379</v>
       </c>
       <c r="L19" t="n">
-        <v>1.134</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.471</v>
+        <v>-0.5692</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7168</v>
+        <v>-1.3773</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7542</v>
+        <v>0.8081</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7496</v>
+        <v>0.2648</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4552</v>
+        <v>0.0297</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2945</v>
+        <v>0.2351</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. DÍAZ JIMÉNEZ</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8901</v>
+        <v>-1.1625</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0024</v>
+        <v>-1.6309</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8877</v>
+        <v>0.4684</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9953</v>
+        <v>-1.5858</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1471</v>
+        <v>-0.5874</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8482</v>
+        <v>-0.9984</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3065</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3469</v>
+        <v>0.7201</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>-0.0533</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6889</v>
+        <v>-2.2526</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1998</v>
+        <v>-1.3075</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8887</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5778</v>
+        <v>0.5916</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3041</v>
+        <v>-0.1993</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2737</v>
+        <v>0.7909</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3321</v>
+        <v>0.2224</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3321</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3003</v>
+        <v>-1.7305</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8156</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5153</v>
+        <v>-1.2261</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7913</v>
+        <v>-2.4535</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3241</v>
+        <v>-1.8333</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1155</v>
+        <v>-0.6202</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4875</v>
+        <v>1.0176</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0875</v>
+        <v>-0.1164</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.575</v>
+        <v>1.134</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3038</v>
+        <v>-3.471</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7634</v>
+        <v>-1.7168</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5405</v>
+        <v>-1.7542</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1589</v>
+        <v>-0.7496</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3747</v>
+        <v>-0.4552</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5336</v>
+        <v>-0.2945</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>P. DIAZ JIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9137</v>
+        <v>-1.8901</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9077</v>
+        <v>-1.0024</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0061</v>
+        <v>-0.8877</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8682</v>
+        <v>-2.9953</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4508</v>
+        <v>-1.1471</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4175</v>
+        <v>-1.8482</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2996</v>
+        <v>-1.3065</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0614</v>
+        <v>-1.3469</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.361</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5686</v>
+        <v>-1.6889</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5121</v>
+        <v>0.1998</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9435</v>
+        <v>-1.8887</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0455</v>
+        <v>0.5778</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6313</v>
+        <v>0.3041</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4142</v>
+        <v>0.2737</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7743</v>
+        <v>-2.9137</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5013</v>
+        <v>-2.9077</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.273</v>
+        <v>-0.0061</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.7551</v>
+        <v>-1.8682</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.6069</v>
+        <v>-1.4508</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1482</v>
+        <v>-0.4175</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0329</v>
+        <v>-1.2996</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.3459</v>
+        <v>0.0614</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6869</v>
+        <v>-1.361</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7223</v>
+        <v>-0.5686</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.2609</v>
+        <v>-1.5121</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5387</v>
+        <v>0.9435</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3441</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9959</v>
+        <v>-1.0455</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5969</v>
+        <v>-0.6313</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.399</v>
+        <v>-0.4142</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.2213</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.7366</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5153</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.7123</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.1155</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.4085</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.1665</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2.575</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.3038</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.7634</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.5405</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.3747</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5336</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. JUAREZ GIMENEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.7743</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.5013</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.273</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.7551</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-4.6069</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.0329</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.3459</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6869</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.7223</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-2.2609</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.9959</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.5969</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.399</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.1052</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484230_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-10.8288</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>-11.8412</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>1.0122</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>-14.8817</v>
       </c>
-      <c r="H24" t="n">
-        <v>-11.5084</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H26" t="n">
+        <v>-11.5083</v>
+      </c>
+      <c r="I26" t="n">
         <v>-3.3734</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>-3.1714</v>
       </c>
-      <c r="K24" t="n">
-        <v>0.1942999999999997</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K26" t="n">
+        <v>0.1943000000000006</v>
+      </c>
+      <c r="L26" t="n">
         <v>-3.3655</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-11.7103</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-11.7024</v>
       </c>
-      <c r="O24" t="n">
-        <v>-0.008000000000000451</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="O26" t="n">
+        <v>-0.008000000000000229</v>
+      </c>
+      <c r="P26" t="n">
         <v>3.9068</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>15.6274</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-1.0727</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-2.2686</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>1.1958</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>1.2186</v>
       </c>
-      <c r="W24" t="n">
-        <v>5.319199999999999</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="W26" t="n">
+        <v>5.3192</v>
+      </c>
+      <c r="X26" t="n">
         <v>-4.1006</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
